--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w9y42eh</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1092</v>
+        <v>134</v>
       </c>
       <c r="Q2" t="n">
-        <v>845</v>
+        <v>751</v>
       </c>
       <c r="R2" t="n">
-        <v>1937</v>
+        <v>885</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1441</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>1056</v>
+        <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>2497</v>
+        <v>1939</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -771,13 +771,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1420</v>
+        <v>1441</v>
       </c>
       <c r="Q4" t="n">
-        <v>1520</v>
+        <v>1056</v>
       </c>
       <c r="R4" t="n">
-        <v>2940</v>
+        <v>2497</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -869,13 +869,13 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
+          <t>https://talk.naver.com/ct/w4pm77</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1613</v>
+        <v>1420</v>
       </c>
       <c r="Q5" t="n">
-        <v>1750</v>
+        <v>1520</v>
       </c>
       <c r="R5" t="n">
-        <v>3363</v>
+        <v>2940</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1465</v>
+        <v>1613</v>
       </c>
       <c r="Q6" t="n">
-        <v>1419</v>
+        <v>1750</v>
       </c>
       <c r="R6" t="n">
-        <v>2884</v>
+        <v>3363</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1049,39 +1049,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>마블피트니스 헬스&amp;PT 해운대점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>hyoyoung0202@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>0507-1384-2203</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>https://blog.naver.com/hyoyoung0202</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2079</v>
+        <v>1465</v>
       </c>
       <c r="Q7" t="n">
-        <v>140</v>
+        <v>1419</v>
       </c>
       <c r="R7" t="n">
-        <v>2219</v>
+        <v>2884</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>1774469002</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/1774469002</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스에프짐 명지점</t>
+          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sf_gym@naver.com</t>
+          <t>skygym21@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1403-1474</t>
+          <t>0507-1473-5661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 강서구 명지국제1로 60-1 10층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/s.f_gym</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4574z</t>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>941</v>
+        <v>2079</v>
       </c>
       <c r="Q8" t="n">
-        <v>545</v>
+        <v>140</v>
       </c>
       <c r="R8" t="n">
-        <v>1486</v>
+        <v>2219</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1154395745</t>
+          <t>1429668350</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154395745</t>
+          <t>https://m.place.naver.com/place/1429668350</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>맨하탄 필라테스&amp;헬스</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1383-9711</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45s2w</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1307,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>464</v>
+        <v>941</v>
       </c>
       <c r="Q9" t="n">
-        <v>201</v>
+        <v>545</v>
       </c>
       <c r="R9" t="n">
-        <v>665</v>
+        <v>1486</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>11663411</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663411</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>노블짐 PT&amp;헬스</t>
+          <t>맨하탄 필라테스&amp;헬스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>koreakorea7754@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1495-9017</t>
+          <t>0507-1383-9711</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 남구 용호로 187-2 노블짐 3층 전체</t>
+          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/koreakorea7754</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w451sf</t>
+          <t>https://talk.naver.com/ct/w45s2w</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1405,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>295</v>
+        <v>464</v>
       </c>
       <c r="Q10" t="n">
-        <v>393</v>
+        <v>201</v>
       </c>
       <c r="R10" t="n">
-        <v>688</v>
+        <v>665</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1231483955</t>
+          <t>11663411</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231483955</t>
+          <t>https://m.place.naver.com/place/11663411</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w9y42eh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="Q3" t="n">
         <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산광역시 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1054,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>inthegym05@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1458-3783</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://www.instagram.com/inthegym05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1071,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1465</v>
+        <v>1077</v>
       </c>
       <c r="Q7" t="n">
-        <v>1419</v>
+        <v>334</v>
       </c>
       <c r="R7" t="n">
-        <v>2884</v>
+        <v>1411</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>1533075467</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/1533075467</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1169,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산광역시 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1245,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스에프짐 명지점</t>
+          <t>맨하탄 필라테스&amp;헬스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sf_gym@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1403-1474</t>
+          <t>0507-1383-9711</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 강서구 명지국제1로 60-1 10층</t>
+          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/s.f_gym</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1269,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4574z</t>
+          <t>https://talk.naver.com/ct/w45s2w</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1279,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>941</v>
+        <v>464</v>
       </c>
       <c r="Q9" t="n">
-        <v>545</v>
+        <v>201</v>
       </c>
       <c r="R9" t="n">
-        <v>1486</v>
+        <v>665</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1298,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1154395745</t>
+          <t>11663411</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154395745</t>
+          <t>https://m.place.naver.com/place/11663411</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1315,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>맨하탄 필라테스&amp;헬스</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1383-9711</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
+          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,19 +1357,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45s2w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1405,17 +1373,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>464</v>
+        <v>1154</v>
       </c>
       <c r="Q10" t="n">
-        <v>201</v>
+        <v>431</v>
       </c>
       <c r="R10" t="n">
-        <v>665</v>
+        <v>1585</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1392,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>11663411</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663411</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1409,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,12 +1461,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1154</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>431</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1585</v>
+        <v>5</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,15 +1490,109 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>awdxasd@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1392-8113</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ntf_suyeong</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>362</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>354</v>
+      </c>
+      <c r="R12" t="n">
+        <v>716</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1886402536</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1886402536</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w9y42eh</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -685,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>O</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="Q3" t="n">
         <v>847</v>
       </c>
       <c r="R3" t="n">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 21 5층,6층</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pm77</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="Q6" t="n">
         <v>1750</v>
       </c>
       <c r="R6" t="n">
-        <v>3363</v>
+        <v>3364</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
+          <t>부산 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wx7kwg3</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="Q7" t="n">
         <v>334</v>
       </c>
       <c r="R7" t="n">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1145,7 +1169,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장평로 440 5층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1337,7 +1365,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1362,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v19w</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1409,34 +1441,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>healthstargym01@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1395-8189</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 금정구 구서로 12 2층 헬스스타짐 구서점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://blog.naver.com/healthstargym01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1451,37 +1483,33 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,109 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>2086997985</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/2086997985</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>awdxasd@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1392-8113</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>부산광역시 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ntf_suyeong</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>362</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>354</v>
-      </c>
-      <c r="R12" t="n">
-        <v>716</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1886402536</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1886402536</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -422,7 +422,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일레븐핏 부산대점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>elevenfit@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1495-7982</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elevenfit</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9y42eh</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>1093</v>
       </c>
       <c r="Q2" t="n">
-        <v>751</v>
+        <v>847</v>
       </c>
       <c r="R2" t="n">
-        <v>885</v>
+        <v>1940</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1356064248</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -662,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1093</v>
+        <v>1441</v>
       </c>
       <c r="Q3" t="n">
-        <v>847</v>
+        <v>1056</v>
       </c>
       <c r="R3" t="n">
-        <v>1940</v>
+        <v>2497</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -771,13 +771,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w4pm77</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1441</v>
+        <v>1420</v>
       </c>
       <c r="Q4" t="n">
-        <v>1056</v>
+        <v>1520</v>
       </c>
       <c r="R4" t="n">
-        <v>2497</v>
+        <v>2940</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -869,13 +869,13 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1420</v>
+        <v>1614</v>
       </c>
       <c r="Q5" t="n">
-        <v>1520</v>
+        <v>1750</v>
       </c>
       <c r="R5" t="n">
-        <v>2940</v>
+        <v>3364</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>inthegym05@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1458-3783</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/inthegym05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
+          <t>https://talk.naver.com/ct/wx7kwg3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1614</v>
+        <v>1079</v>
       </c>
       <c r="Q6" t="n">
-        <v>1750</v>
+        <v>334</v>
       </c>
       <c r="R6" t="n">
-        <v>3364</v>
+        <v>1413</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,56 +1032,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1533075467</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1533075467</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
+          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>inthegym05@naver.com</t>
+          <t>skygym21@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1458-3783</t>
+          <t>0507-1473-5661</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 동래구 아시아드대로 239-1 5층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inthegym05</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wx7kwg3</t>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1079</v>
+        <v>2079</v>
       </c>
       <c r="Q7" t="n">
-        <v>334</v>
+        <v>140</v>
       </c>
       <c r="R7" t="n">
-        <v>1413</v>
+        <v>2219</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1533075467</t>
+          <t>1429668350</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533075467</t>
+          <t>https://m.place.naver.com/place/1429668350</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1152,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2079</v>
+        <v>941</v>
       </c>
       <c r="Q8" t="n">
-        <v>140</v>
+        <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>2219</v>
+        <v>1486</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1434,41 +1434,41 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>healthstargym01@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1395-8189</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 금정구 구서로 12 2층 헬스스타짐 구서점</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthstargym01</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,33 +1483,37 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>230</v>
+        <v>5</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2086997985</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086997985</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -426,13 +426,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -726,10 +718,10 @@
         <v>1441</v>
       </c>
       <c r="Q3" t="n">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="R3" t="n">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산광역시 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 동래구 아시아드대로 239-1 5층</t>
+          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wx7kwg3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1020,10 +1000,10 @@
         <v>1079</v>
       </c>
       <c r="Q6" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="R6" t="n">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1071,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산광역시 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1169,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 강서구 명지국제1로 60-1 10층</t>
+          <t>부산광역시 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4574z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1245,34 +1217,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>맨하탄 필라테스&amp;헬스</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1383-9711</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
+          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,19 +1259,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45s2w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1307,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>464</v>
+        <v>1153</v>
       </c>
       <c r="Q9" t="n">
-        <v>201</v>
+        <v>431</v>
       </c>
       <c r="R9" t="n">
-        <v>665</v>
+        <v>1584</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>11663411</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663411</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산광역시 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1390,17 +1358,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1154</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>431</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>1585</v>
+        <v>5</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>awdxasd@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1392-8113</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://www.instagram.com/ntf_suyeong</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,12 +1457,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
+          <t>https://talk.naver.com/ct/w4uzzh</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1471,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>362</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>354</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1486,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1886402536</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1886402536</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -422,17 +422,17 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>O</t>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4h77f</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="Q3" t="n">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="R3" t="n">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 21 5층,6층</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pm77</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -906,10 +922,10 @@
         <v>1614</v>
       </c>
       <c r="Q5" t="n">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="R5" t="n">
-        <v>3364</v>
+        <v>3365</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
+          <t>부산 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wx7kwg3</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q6" t="n">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R6" t="n">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1051,7 +1071,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 장평로 440 5층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1061,7 +1081,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,15 +1091,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1094,10 +1118,10 @@
         <v>2079</v>
       </c>
       <c r="Q7" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R7" t="n">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1123,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스에프짐 명지점</t>
+          <t>맨하탄 필라테스&amp;헬스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sf_gym@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1403-1474</t>
+          <t>0507-1383-9711</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 강서구 명지국제1로 60-1 10층</t>
+          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/s.f_gym</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45s2w</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>941</v>
+        <v>464</v>
       </c>
       <c r="Q8" t="n">
-        <v>545</v>
+        <v>201</v>
       </c>
       <c r="R8" t="n">
-        <v>1486</v>
+        <v>665</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1154395745</t>
+          <t>11663411</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154395745</t>
+          <t>https://m.place.naver.com/place/11663411</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1239,7 +1267,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v19w</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1282,10 +1314,10 @@
         <v>1153</v>
       </c>
       <c r="Q9" t="n">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="R9" t="n">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1311,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>awdxasd@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1392-8113</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://www.instagram.com/ntf_suyeong</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,13 +1390,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4uzzh</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>362</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>354</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1886402536</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1886402536</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
+          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>awdxasd@naver.com</t>
+          <t>healthstargym01@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1392-8113</t>
+          <t>0507-1395-8189</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
+          <t>부산 금정구 구서로 12 2층 헬스스타짐 구서점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ntf_suyeong</t>
+          <t>https://blog.naver.com/healthstargym01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,19 +1483,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4uzzh</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>362</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="n">
-        <v>354</v>
+        <v>151</v>
       </c>
       <c r="R11" t="n">
-        <v>716</v>
+        <v>231</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1486,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1886402536</t>
+          <t>2086997985</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886402536</t>
+          <t>https://m.place.naver.com/place/2086997985</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="41" customWidth="1" min="8" max="8"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -581,12 +581,12 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="Q2" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="R2" t="n">
         <v>1940</v>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="Q3" t="n">
         <v>1056</v>
       </c>
       <c r="R3" t="n">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산광역시 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="Q4" t="n">
         <v>1520</v>
       </c>
       <c r="R4" t="n">
-        <v>2940</v>
+        <v>2943</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="Q5" t="n">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="R5" t="n">
-        <v>3365</v>
+        <v>3367</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 동래구 아시아드대로 239-1 5층</t>
+          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inthegym05</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="Q6" t="n">
         <v>336</v>
       </c>
       <c r="R6" t="n">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1140,41 +1140,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>맨하탄 필라테스&amp;헬스</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1383-9711</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
+          <t>부산광역시 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1194,14 +1194,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45s2w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>464</v>
+        <v>729</v>
       </c>
       <c r="Q8" t="n">
-        <v>201</v>
+        <v>492</v>
       </c>
       <c r="R8" t="n">
-        <v>665</v>
+        <v>1221</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>11663411</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663411</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산광역시 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1292,14 +1288,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1311,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1153</v>
+        <v>943</v>
       </c>
       <c r="Q9" t="n">
-        <v>432</v>
+        <v>545</v>
       </c>
       <c r="R9" t="n">
-        <v>1585</v>
+        <v>1488</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,51 +1318,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
+          <t>맨하탄 필라테스&amp;헬스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>awdxasd@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1392-8113</t>
+          <t>0507-1383-9711</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
+          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ntf_suyeong</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4uzzh</t>
+          <t>https://talk.naver.com/ct/w45s2w</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1397,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>362</v>
+        <v>465</v>
       </c>
       <c r="Q10" t="n">
-        <v>354</v>
+        <v>201</v>
       </c>
       <c r="R10" t="n">
-        <v>716</v>
+        <v>666</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,51 +1416,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1886402536</t>
+          <t>11663411</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886402536</t>
+          <t>https://m.place.naver.com/place/11663411</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
+          <t>노블짐 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>healthstargym01@naver.com</t>
+          <t>koreakorea7754@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1395-8189</t>
+          <t>0507-1495-9017</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 금정구 구서로 12 2층 헬스스타짐 구서점</t>
+          <t>부산광역시 남구 용호로 187-2 노블짐 3층 전체</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthstargym01</t>
+          <t>https://blog.naver.com/koreakorea7754</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1499,17 +1491,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
+        <v>295</v>
       </c>
       <c r="Q11" t="n">
-        <v>151</v>
+        <v>393</v>
       </c>
       <c r="R11" t="n">
-        <v>231</v>
+        <v>688</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1510,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2086997985</t>
+          <t>1231483955</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086997985</t>
+          <t>https://m.place.naver.com/place/1231483955</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -426,8 +426,8 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w9y42eh</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1092</v>
+        <v>134</v>
       </c>
       <c r="Q2" t="n">
-        <v>848</v>
+        <v>751</v>
       </c>
       <c r="R2" t="n">
-        <v>1940</v>
+        <v>885</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1445</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>1056</v>
+        <v>849</v>
       </c>
       <c r="R3" t="n">
-        <v>2501</v>
+        <v>1941</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>멋짐 서면점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -771,18 +771,18 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1314-8689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 21 5층,6층</t>
+          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,12 +792,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
+          <t>https://talk.naver.com/ct/w4h77f</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1423</v>
+        <v>1446</v>
       </c>
       <c r="Q4" t="n">
-        <v>1520</v>
+        <v>1057</v>
       </c>
       <c r="R4" t="n">
-        <v>2943</v>
+        <v>2503</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1024587035</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1024587035</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -869,18 +869,18 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
+          <t>https://talk.naver.com/ct/w4pm77</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1615</v>
+        <v>1423</v>
       </c>
       <c r="Q5" t="n">
-        <v>1752</v>
+        <v>1521</v>
       </c>
       <c r="R5" t="n">
-        <v>3367</v>
+        <v>2944</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>inthegym05@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1458-3783</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 동래구 아시아드대로 239-1 5층</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wx7kwg3</t>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1083</v>
+        <v>1619</v>
       </c>
       <c r="Q6" t="n">
-        <v>336</v>
+        <v>1754</v>
       </c>
       <c r="R6" t="n">
-        <v>1419</v>
+        <v>3373</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1533075467</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533075467</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1049,39 +1049,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>inthegym05@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>0507-1458-3783</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>https://www.instagram.com/inthegym05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
+          <t>https://talk.naver.com/ct/wx7kwg3</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2079</v>
+        <v>1084</v>
       </c>
       <c r="Q7" t="n">
-        <v>141</v>
+        <v>337</v>
       </c>
       <c r="R7" t="n">
-        <v>2220</v>
+        <v>1421</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>1533075467</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/1533075467</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,39 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>헬짐 HELL GYM</t>
+          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hellgymseomyeon@naver.com</t>
+          <t>skygym21@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1435-7378</t>
+          <t>0507-1473-5661</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
+          <t>부산 사하구 장평로 440 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgymseomyeon</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1194,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wqbu4w7</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>729</v>
+        <v>2079</v>
       </c>
       <c r="Q8" t="n">
-        <v>492</v>
+        <v>141</v>
       </c>
       <c r="R8" t="n">
-        <v>1221</v>
+        <v>2220</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1847755059</t>
+          <t>1429668350</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847755059</t>
+          <t>https://m.place.naver.com/place/1429668350</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1246,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스에프짐 명지점</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sf_gym@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1403-1474</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 강서구 명지국제1로 60-1 10층</t>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/s.f_gym</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1288,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v19w</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1303,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>943</v>
+        <v>1152</v>
       </c>
       <c r="Q9" t="n">
-        <v>545</v>
+        <v>432</v>
       </c>
       <c r="R9" t="n">
-        <v>1488</v>
+        <v>1584</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1154395745</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154395745</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>맨하탄 필라테스&amp;헬스</t>
+          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>healthstargym01@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1383-9711</t>
+          <t>0507-1395-8189</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
+          <t>부산 금정구 구서로 12 2층 헬스스타짐 구서점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>https://blog.naver.com/healthstargym01</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1382,14 +1390,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w45s2w</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>465</v>
+        <v>80</v>
       </c>
       <c r="Q10" t="n">
-        <v>201</v>
+        <v>152</v>
       </c>
       <c r="R10" t="n">
-        <v>666</v>
+        <v>232</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>11663411</t>
+          <t>2086997985</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663411</t>
+          <t>https://m.place.naver.com/place/2086997985</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>노블짐 PT&amp;헬스</t>
+          <t>JG스포츠재활운동센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>koreakorea7754@naver.com</t>
+          <t>jgmovelab@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1495-9017</t>
+          <t>051-611-7772</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 남구 용호로 187-2 노블짐 3층 전체</t>
+          <t>부산 남구 못골로 49 글로리마트 3층 JG스포츠재활운동센터</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/koreakorea7754</t>
+          <t>https://blog.naver.com/jgmovelab</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w3jm5cv</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1495,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>295</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
-        <v>393</v>
+        <v>277</v>
       </c>
       <c r="R11" t="n">
-        <v>688</v>
+        <v>297</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1510,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1231483955</t>
+          <t>1179468470</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1231483955</t>
+          <t>https://m.place.naver.com/place/1179468470</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>일레븐핏 부산대점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>elevenfit@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1495-7982</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elevenfit</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w9y42eh</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>134</v>
+        <v>1092</v>
       </c>
       <c r="Q2" t="n">
-        <v>751</v>
+        <v>849</v>
       </c>
       <c r="R2" t="n">
-        <v>885</v>
+        <v>1941</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1356064248</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w4pm77</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1092</v>
+        <v>1423</v>
       </c>
       <c r="Q3" t="n">
-        <v>849</v>
+        <v>1521</v>
       </c>
       <c r="R3" t="n">
-        <v>1941</v>
+        <v>2944</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,17 +738,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 서면점</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -771,13 +771,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1314-8689</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 부산진구 서전로9번길 20 헤도인파크에비뉴 2층</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4h77f</t>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1446</v>
+        <v>1619</v>
       </c>
       <c r="Q4" t="n">
-        <v>1057</v>
+        <v>1754</v>
       </c>
       <c r="R4" t="n">
-        <v>2503</v>
+        <v>3373</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +836,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1024587035</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024587035</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>inthegym05@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1458-3783</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://www.instagram.com/inthegym05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
+          <t>https://talk.naver.com/ct/wx7kwg3</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1423</v>
+        <v>1085</v>
       </c>
       <c r="Q5" t="n">
-        <v>1521</v>
+        <v>337</v>
       </c>
       <c r="R5" t="n">
-        <v>2944</v>
+        <v>1422</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1533075467</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1533075467</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1619</v>
+        <v>477</v>
       </c>
       <c r="Q6" t="n">
-        <v>1754</v>
+        <v>158</v>
       </c>
       <c r="R6" t="n">
-        <v>3373</v>
+        <v>635</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>inthegym05@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1458-3783</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 동래구 아시아드대로 239-1 5층</t>
+          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inthegym05</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,19 +1091,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wx7kwg3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1084</v>
+        <v>729</v>
       </c>
       <c r="Q7" t="n">
-        <v>337</v>
+        <v>493</v>
       </c>
       <c r="R7" t="n">
-        <v>1421</v>
+        <v>1222</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1533075467</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533075467</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,34 +1148,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스카이짐24H &amp; 기구필라테스 &amp; GDR골프</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>skygym21@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1473-5661</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 사하구 장평로 440 5층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wqbu4w7</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2079</v>
+        <v>945</v>
       </c>
       <c r="Q8" t="n">
-        <v>141</v>
+        <v>545</v>
       </c>
       <c r="R8" t="n">
-        <v>2220</v>
+        <v>1490</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1429668350</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1429668350</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>맨하탄 필라테스&amp;헬스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1383-9711</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
+          <t>https://talk.naver.com/ct/w45s2w</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1152</v>
+        <v>465</v>
       </c>
       <c r="Q9" t="n">
-        <v>432</v>
+        <v>201</v>
       </c>
       <c r="R9" t="n">
-        <v>1584</v>
+        <v>666</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>11663411</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/11663411</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>healthstargym01@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1395-8189</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 금정구 구서로 12 2층 헬스스타짐 구서점</t>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthstargym01</t>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,15 +1381,19 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v19w</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>80</v>
+        <v>1152</v>
       </c>
       <c r="Q10" t="n">
-        <v>152</v>
+        <v>433</v>
       </c>
       <c r="R10" t="n">
-        <v>232</v>
+        <v>1585</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2086997985</t>
+          <t>1652983472</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086997985</t>
+          <t>https://m.place.naver.com/place/1652983472</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JG스포츠재활운동센터</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jgmovelab@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>051-611-7772</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산 남구 못골로 49 글로리마트 3층 JG스포츠재활운동센터</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jgmovelab</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w3jm5cv</t>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="Q11" t="n">
-        <v>277</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>297</v>
+        <v>5</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1179468470</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179468470</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/부산_PT.xlsx
+++ b/naver-place-crawler/results_health/부산_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fmpt__teddy@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1343-6817</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
+          <t>부산 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sksoe31e</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4fpwi</t>
+          <t>https://talk.naver.com/ct/w9y42eh</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1092</v>
+        <v>134</v>
       </c>
       <c r="Q2" t="n">
-        <v>849</v>
+        <v>751</v>
       </c>
       <c r="R2" t="n">
-        <v>1941</v>
+        <v>885</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1138689357</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138689357</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 연산점</t>
+          <t>피트니스스퀘어 헬스&amp;PT&amp;기구필라테스 서면점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mutgym8689@naver.com</t>
+          <t>fmpt__teddy@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1409-8689</t>
+          <t>0507-1343-6817</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 연제구 반송로 21 5층,6층</t>
+          <t>부산 부산진구 동천로 70 서면쌍용플래티넘상가 3층 피트니스스퀘어 서면 헬스</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym8689</t>
+          <t>https://open.kakao.com/o/sksoe31e</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm77</t>
+          <t>https://talk.naver.com/ct/w4fpwi</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1423</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="n">
-        <v>1521</v>
+        <v>849</v>
       </c>
       <c r="R3" t="n">
-        <v>2944</v>
+        <v>1941</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1868714041</t>
+          <t>1138689357</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1868714041</t>
+          <t>https://m.place.naver.com/place/1138689357</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 동래점</t>
+          <t>멋짐 헬스&amp;PT 연산점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -771,13 +771,13 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1355-8689</t>
+          <t>0507-1409-8689</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
+          <t>부산 연제구 반송로 21 5층,6층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4pm7n</t>
+          <t>https://talk.naver.com/ct/w4pm77</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1619</v>
+        <v>1423</v>
       </c>
       <c r="Q4" t="n">
-        <v>1754</v>
+        <v>1521</v>
       </c>
       <c r="R4" t="n">
-        <v>3373</v>
+        <v>2944</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1261115217</t>
+          <t>1868714041</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1261115217</t>
+          <t>https://m.place.naver.com/place/1868714041</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
+          <t>멋짐 헬스&amp;PT 동래점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inthegym05@naver.com</t>
+          <t>mutgym8689@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1458-3783</t>
+          <t>0507-1355-8689</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 동래구 아시아드대로 239-1 5층</t>
+          <t>부산 동래구 명륜로103번길 8 스카이뷰 4층, 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/inthegym05</t>
+          <t>https://blog.naver.com/mutgym8689</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wx7kwg3</t>
+          <t>https://talk.naver.com/ct/w4pm7n</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1085</v>
+        <v>1619</v>
       </c>
       <c r="Q5" t="n">
-        <v>337</v>
+        <v>1754</v>
       </c>
       <c r="R5" t="n">
-        <v>1422</v>
+        <v>3373</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1533075467</t>
+          <t>1261115217</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533075467</t>
+          <t>https://m.place.naver.com/place/1261115217</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>인더짐 헬스&amp;스피닝&amp;PT 동래미남역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>inthegym05@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1458-3783</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 동래구 아시아드대로 239-1 5층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://www.instagram.com/inthegym05</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4o8qo</t>
+          <t>https://talk.naver.com/ct/wx7kwg3</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>477</v>
+        <v>1085</v>
       </c>
       <c r="Q6" t="n">
-        <v>158</v>
+        <v>337</v>
       </c>
       <c r="R6" t="n">
-        <v>635</v>
+        <v>1422</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1533075467</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1533075467</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬짐 HELL GYM</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hellgymseomyeon@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1435-7378</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hellgymseomyeon</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>729</v>
+        <v>477</v>
       </c>
       <c r="Q7" t="n">
-        <v>493</v>
+        <v>158</v>
       </c>
       <c r="R7" t="n">
-        <v>1222</v>
+        <v>635</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1847755059</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1847755059</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1143,34 +1147,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에스에프짐 명지점</t>
+          <t>헬짐 HELL GYM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sf_gym@naver.com</t>
+          <t>hellgymseomyeon@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1403-1474</t>
+          <t>0507-1435-7378</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 강서구 명지국제1로 60-1 10층</t>
+          <t>부산 부산진구 전포대로199번길 15 현대오피스텔 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/s.f_gym</t>
+          <t>https://blog.naver.com/hellgymseomyeon</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,19 +1189,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4574z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>945</v>
+        <v>729</v>
       </c>
       <c r="Q8" t="n">
-        <v>545</v>
+        <v>493</v>
       </c>
       <c r="R8" t="n">
-        <v>1490</v>
+        <v>1222</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1154395745</t>
+          <t>1847755059</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1154395745</t>
+          <t>https://m.place.naver.com/place/1847755059</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>맨하탄 필라테스&amp;헬스</t>
+          <t>에스에프짐 명지점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>sf_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1383-9711</t>
+          <t>0507-1403-1474</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
+          <t>부산 강서구 명지국제1로 60-1 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>http://www.instagram.com/s.f_gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45s2w</t>
+          <t>https://talk.naver.com/ct/w4574z</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>465</v>
+        <v>945</v>
       </c>
       <c r="Q9" t="n">
-        <v>201</v>
+        <v>545</v>
       </c>
       <c r="R9" t="n">
-        <v>666</v>
+        <v>1490</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>11663411</t>
+          <t>1154395745</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663411</t>
+          <t>https://m.place.naver.com/place/1154395745</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,34 +1339,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>빅스짐 하단점 헬스 PT</t>
+          <t>맨하탄 필라테스&amp;헬스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bigsgym20@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1357-6662</t>
+          <t>0507-1383-9711</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 사하구 낙동대로457번길 5 301호</t>
+          <t>부산 금정구 중앙대로1841번길 23 현대타운 8층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_hadan</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v19w</t>
+          <t>https://talk.naver.com/ct/w45s2w</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1152</v>
+        <v>465</v>
       </c>
       <c r="Q10" t="n">
-        <v>433</v>
+        <v>201</v>
       </c>
       <c r="R10" t="n">
-        <v>1585</v>
+        <v>666</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1652983472</t>
+          <t>11663411</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652983472</t>
+          <t>https://m.place.naver.com/place/11663411</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,96 +1437,194 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>빅스짐 하단점 헬스 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>bigsgym20@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1357-6662</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>부산 사하구 낙동대로457번길 5 301호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bigsgym_hadan</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v19w</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1152</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>433</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1585</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1652983472</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1652983472</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>언로드 PT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>unloadpt@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1320-4232</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>2024136684</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
